--- a/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0001T0006Z000C1N18_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0001T0006Z000C1N18_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>35.0169116282261</v>
+        <v>5.690248139586741</v>
       </c>
       <c r="D2" t="n">
-        <v>65.9411181740975</v>
+        <v>10.71543170329084</v>
       </c>
       <c r="E2" t="n">
-        <v>17.65688891242328</v>
+        <v>2.869244448268783</v>
       </c>
       <c r="F2" t="n">
-        <v>20.27109379814929</v>
+        <v>3.294052742199261</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>47.61611172100866</v>
+        <v>7.737618154663908</v>
       </c>
       <c r="D3" t="n">
-        <v>48.46590207425602</v>
+        <v>7.875709087066604</v>
       </c>
       <c r="E3" t="n">
-        <v>17.65688891242328</v>
+        <v>2.869244448268783</v>
       </c>
       <c r="F3" t="n">
-        <v>20.27109379814929</v>
+        <v>3.294052742199261</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>57.1036128934075</v>
+        <v>9.27933709517872</v>
       </c>
       <c r="D4" t="n">
-        <v>58.56378890661555</v>
+        <v>9.516615697325028</v>
       </c>
       <c r="E4" t="n">
-        <v>17.65688891242328</v>
+        <v>2.869244448268783</v>
       </c>
       <c r="F4" t="n">
-        <v>20.27109379814929</v>
+        <v>3.294052742199261</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>39.90118829804138</v>
+        <v>6.483943098431725</v>
       </c>
       <c r="D5" t="n">
-        <v>39.51095654408243</v>
+        <v>6.420530438413395</v>
       </c>
       <c r="E5" t="n">
-        <v>17.65688891242328</v>
+        <v>2.869244448268783</v>
       </c>
       <c r="F5" t="n">
-        <v>20.27109379814929</v>
+        <v>3.294052742199261</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>65.75588468260558</v>
+        <v>10.68533126092341</v>
       </c>
       <c r="D6" t="n">
-        <v>67.55211345654459</v>
+        <v>10.9772184366885</v>
       </c>
       <c r="E6" t="n">
-        <v>17.65688891242328</v>
+        <v>2.869244448268783</v>
       </c>
       <c r="F6" t="n">
-        <v>20.27109379814929</v>
+        <v>3.294052742199261</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>45.44524345597492</v>
+        <v>7.384852061595924</v>
       </c>
       <c r="D7" t="n">
-        <v>45.30594276462121</v>
+        <v>7.362215699250946</v>
       </c>
       <c r="E7" t="n">
-        <v>17.65688891242328</v>
+        <v>2.869244448268783</v>
       </c>
       <c r="F7" t="n">
-        <v>20.27109379814929</v>
+        <v>3.294052742199261</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>18.95015277364935</v>
+        <v>3.07939982571802</v>
       </c>
       <c r="D8" t="n">
-        <v>18.5174310453889</v>
+        <v>3.009082544875697</v>
       </c>
       <c r="E8" t="n">
-        <v>17.65688891242328</v>
+        <v>2.869244448268783</v>
       </c>
       <c r="F8" t="n">
-        <v>20.27109379814929</v>
+        <v>3.294052742199261</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>22.10912491622361</v>
+        <v>3.592732798886336</v>
       </c>
       <c r="D9" t="n">
-        <v>21.77565604643819</v>
+        <v>3.538544107546205</v>
       </c>
       <c r="E9" t="n">
-        <v>17.65688891242328</v>
+        <v>2.869244448268783</v>
       </c>
       <c r="F9" t="n">
-        <v>20.27109379814929</v>
+        <v>3.294052742199261</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>8.080488820947146</v>
+        <v>1.313079433403911</v>
       </c>
       <c r="D10" t="n">
-        <v>7.635654822338897</v>
+        <v>1.240793908630071</v>
       </c>
       <c r="E10" t="n">
-        <v>17.65688891242328</v>
+        <v>2.869244448268783</v>
       </c>
       <c r="F10" t="n">
-        <v>20.27109379814929</v>
+        <v>3.294052742199261</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
